--- a/Asian Melanoma.xlsx
+++ b/Asian Melanoma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hoangmanhduc\France\Projet d'étude\Meta analysis of melanoma genomic\KQ\bản lưu trữ-JCAD\1 số bản file nháp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDC0874-4AD8-4C2E-9375-E7EB580AF235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A873D77B-AAAA-45A4-A674-E787B8141ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{332B6D4D-EE64-469E-B3F3-4FE594CDDE31}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{332B6D4D-EE64-469E-B3F3-4FE594CDDE31}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthesis" sheetId="20" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <sheet name="Sheet3" sheetId="11" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gene mutation'!$A$2:$GX$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gene mutation'!$A$2:$GX$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet5!$G$60:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synthese articles'!$A$2:$N$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Synthesis!$A$2:$V$49</definedName>
@@ -313,7 +313,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="745">
   <si>
     <t>Author</t>
   </si>
@@ -3396,6 +3396,9 @@
   </si>
   <si>
     <t>Target NGS</t>
+  </si>
+  <si>
+    <t>Min  et al [9], 2019</t>
   </si>
 </sst>
 </file>
@@ -3906,7 +3909,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4466,6 +4469,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel_BuiltIn_Bad" xfId="2" xr:uid="{00687D2E-114A-4421-BB52-6B5F3AA6FB42}"/>
@@ -4473,27 +4479,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 3" xfId="1" xr:uid="{50A82E93-9333-4249-8037-6C0447A8782E}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -15695,7 +15681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801AB4AF-D1C3-48D4-9E65-5B151343A7F4}">
-  <dimension ref="A1:JA56"/>
+  <dimension ref="A1:JA57"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -17499,251 +17485,307 @@
       <c r="IZ4" s="69"/>
       <c r="JA4" s="68"/>
     </row>
-    <row r="5" spans="1:261" s="37" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A5" s="36">
-        <v>17</v>
-      </c>
-      <c r="B5" s="117" t="s">
-        <v>652</v>
-      </c>
-      <c r="C5" s="139" t="s">
+    <row r="5" spans="1:261" ht="28.5" customHeight="1">
+      <c r="A5" s="1">
+        <v>9</v>
+      </c>
+      <c r="B5" s="205" t="s">
+        <v>744</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>655</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G5" s="65">
+        <v>47</v>
+      </c>
+      <c r="H5" s="65">
+        <v>47</v>
+      </c>
+      <c r="I5" s="65">
+        <v>67</v>
+      </c>
+      <c r="J5" s="65">
+        <v>19</v>
+      </c>
+      <c r="K5" s="65">
+        <v>28</v>
+      </c>
+      <c r="L5" s="65">
+        <v>47</v>
+      </c>
+      <c r="M5" s="65">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="161" t="s">
         <v>617</v>
       </c>
-      <c r="D5" s="103" t="s">
-        <v>549</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="G5" s="103">
-        <v>55</v>
-      </c>
-      <c r="H5" s="104">
-        <v>55</v>
-      </c>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="103">
-        <v>55</v>
-      </c>
-      <c r="M5" s="104">
-        <v>55</v>
-      </c>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104" t="s">
-        <v>617</v>
-      </c>
-      <c r="R5" s="105"/>
-      <c r="S5" s="105"/>
-      <c r="T5" s="105"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105"/>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
-      <c r="AA5" s="105"/>
-      <c r="AB5" s="105"/>
-      <c r="AC5" s="105"/>
-      <c r="AD5" s="105"/>
-      <c r="AE5" s="105"/>
-      <c r="AF5" s="106">
-        <v>18</v>
-      </c>
-      <c r="AG5" s="106">
-        <v>18</v>
-      </c>
-      <c r="AH5" s="106"/>
-      <c r="AI5" s="106"/>
-      <c r="AJ5" s="106"/>
-      <c r="AK5" s="106"/>
-      <c r="AL5" s="106"/>
-      <c r="AM5" s="106"/>
-      <c r="AN5" s="106"/>
-      <c r="AO5" s="106"/>
-      <c r="AP5" s="106"/>
-      <c r="AQ5" s="106"/>
-      <c r="AR5" s="106"/>
-      <c r="AS5" s="106"/>
-      <c r="AT5" s="106"/>
-      <c r="AU5" s="106"/>
-      <c r="AV5" s="106"/>
-      <c r="AW5" s="106"/>
-      <c r="AX5" s="106"/>
-      <c r="AY5" s="106"/>
-      <c r="AZ5" s="106"/>
-      <c r="BA5" s="106"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="105"/>
-      <c r="BD5" s="105"/>
-      <c r="BE5" s="105"/>
-      <c r="BF5" s="105"/>
-      <c r="BG5" s="105"/>
-      <c r="BH5" s="105"/>
-      <c r="BI5" s="105"/>
-      <c r="BJ5" s="105"/>
-      <c r="BK5" s="105"/>
-      <c r="BL5" s="105"/>
-      <c r="BM5" s="105"/>
-      <c r="BN5" s="105"/>
-      <c r="BO5" s="105"/>
-      <c r="BP5" s="105"/>
-      <c r="BQ5" s="105"/>
-      <c r="BR5" s="105"/>
-      <c r="BS5" s="105"/>
-      <c r="BT5" s="105"/>
-      <c r="BU5" s="105"/>
-      <c r="BV5" s="105"/>
-      <c r="BW5" s="105"/>
-      <c r="BX5" s="105"/>
-      <c r="BY5" s="105"/>
-      <c r="BZ5" s="105"/>
-      <c r="CA5" s="105"/>
-      <c r="CB5" s="105"/>
-      <c r="CC5" s="105"/>
-      <c r="CD5" s="105"/>
-      <c r="CE5" s="105"/>
-      <c r="CF5" s="105"/>
-      <c r="CG5" s="105"/>
-      <c r="CH5" s="105"/>
-      <c r="CI5" s="105"/>
-      <c r="CJ5" s="105"/>
-      <c r="CK5" s="105"/>
-      <c r="CL5" s="105"/>
-      <c r="CM5" s="105"/>
-      <c r="CN5" s="105"/>
-      <c r="CO5" s="105"/>
-      <c r="CP5" s="105"/>
-      <c r="CQ5" s="105"/>
-      <c r="CR5" s="105"/>
-      <c r="CS5" s="105"/>
-      <c r="CT5" s="105"/>
-      <c r="CU5" s="105"/>
-      <c r="CV5" s="105"/>
-      <c r="CW5" s="105"/>
-      <c r="CX5" s="105"/>
-      <c r="CY5" s="105"/>
-      <c r="CZ5" s="105"/>
-      <c r="DA5" s="105"/>
-      <c r="DB5" s="105"/>
-      <c r="DC5" s="105"/>
-      <c r="DD5" s="105"/>
-      <c r="DE5" s="105"/>
-      <c r="DF5" s="105"/>
-      <c r="DG5" s="105"/>
-      <c r="DH5" s="105"/>
-      <c r="DI5" s="105"/>
-      <c r="DJ5" s="105"/>
-      <c r="DK5" s="105"/>
-      <c r="DL5" s="105"/>
-      <c r="DM5" s="105"/>
-      <c r="DN5" s="105"/>
-      <c r="DO5" s="105"/>
-      <c r="DP5" s="105"/>
-      <c r="DQ5" s="105"/>
-      <c r="DR5" s="105"/>
-      <c r="DS5" s="105"/>
-      <c r="DT5" s="105"/>
-      <c r="DU5" s="105"/>
-      <c r="DV5" s="105"/>
-      <c r="DW5" s="105"/>
-      <c r="DX5" s="105"/>
-      <c r="DY5" s="105"/>
-      <c r="DZ5" s="105"/>
-      <c r="EA5" s="105"/>
-      <c r="EB5" s="105"/>
-      <c r="EC5" s="105"/>
-      <c r="ED5" s="105"/>
-      <c r="EE5" s="105"/>
-      <c r="EF5" s="105"/>
-      <c r="EG5" s="105"/>
-      <c r="EH5" s="105"/>
-      <c r="EI5" s="105"/>
-      <c r="EJ5" s="105"/>
-      <c r="EK5" s="105"/>
-      <c r="EL5" s="105"/>
-      <c r="EM5" s="105"/>
-      <c r="EN5" s="105"/>
-      <c r="EO5" s="105"/>
-      <c r="EP5" s="105"/>
-      <c r="EQ5" s="105"/>
-      <c r="ER5" s="105"/>
-      <c r="ES5" s="105"/>
-      <c r="ET5" s="105"/>
-      <c r="EU5" s="105"/>
-      <c r="EV5" s="105"/>
-      <c r="EW5" s="105"/>
-      <c r="EX5" s="105"/>
-      <c r="EY5" s="105"/>
-      <c r="EZ5" s="105"/>
-      <c r="FA5" s="105"/>
-      <c r="FB5" s="105"/>
-      <c r="FC5" s="105"/>
-      <c r="FD5" s="105"/>
-      <c r="FE5" s="105"/>
-      <c r="FF5" s="105"/>
-      <c r="FG5" s="105"/>
-      <c r="FH5" s="105"/>
-      <c r="FI5" s="105"/>
-      <c r="FJ5" s="105"/>
-      <c r="FK5" s="105"/>
-      <c r="FL5" s="105"/>
-      <c r="FM5" s="105"/>
-      <c r="FN5" s="105"/>
-      <c r="FO5" s="105"/>
-      <c r="FP5" s="105"/>
-      <c r="FQ5" s="105"/>
-      <c r="FR5" s="105"/>
-      <c r="FS5" s="105"/>
-      <c r="FT5" s="105"/>
-      <c r="FU5" s="105"/>
-      <c r="FV5" s="105"/>
-      <c r="FW5" s="105"/>
-      <c r="FX5" s="105"/>
-      <c r="FY5" s="105"/>
-      <c r="FZ5" s="105"/>
-      <c r="GA5" s="105"/>
-      <c r="GB5" s="105"/>
-      <c r="GC5" s="105"/>
-      <c r="GD5" s="105"/>
-      <c r="GE5" s="105"/>
-      <c r="GF5" s="105"/>
-      <c r="GG5" s="105"/>
-      <c r="GH5" s="105"/>
-      <c r="GI5" s="105"/>
-      <c r="GJ5" s="105"/>
-      <c r="GK5" s="105"/>
-      <c r="GL5" s="105"/>
-      <c r="GM5" s="105"/>
-      <c r="GN5" s="105"/>
-      <c r="GO5" s="105"/>
-      <c r="GP5" s="105"/>
-      <c r="GQ5" s="105"/>
-      <c r="GR5" s="105"/>
-      <c r="GS5" s="105"/>
-      <c r="GT5" s="105"/>
-      <c r="GU5" s="105"/>
-      <c r="GV5" s="105"/>
-      <c r="GW5" s="105"/>
-      <c r="GX5" s="105"/>
-      <c r="GY5" s="105"/>
-      <c r="GZ5" s="105"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
+      <c r="AA5" s="68"/>
+      <c r="AB5" s="68"/>
+      <c r="AC5" s="68"/>
+      <c r="AD5" s="68"/>
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
+      <c r="AN5" s="68"/>
+      <c r="AO5" s="68"/>
+      <c r="AP5" s="68"/>
+      <c r="AQ5" s="68"/>
+      <c r="AR5" s="68"/>
+      <c r="AS5" s="68"/>
+      <c r="AT5" s="68"/>
+      <c r="AU5" s="68"/>
+      <c r="AV5" s="68"/>
+      <c r="AW5" s="68"/>
+      <c r="AX5" s="68"/>
+      <c r="AY5" s="68"/>
+      <c r="AZ5" s="68"/>
+      <c r="BA5" s="68"/>
+      <c r="BB5" s="68"/>
+      <c r="BC5" s="68"/>
+      <c r="BD5" s="68"/>
+      <c r="BE5" s="68"/>
+      <c r="BF5" s="68"/>
+      <c r="BG5" s="68"/>
+      <c r="BH5" s="68"/>
+      <c r="BI5" s="68"/>
+      <c r="BJ5" s="68"/>
+      <c r="BK5" s="68"/>
+      <c r="BL5" s="68"/>
+      <c r="BM5" s="68"/>
+      <c r="BN5" s="68"/>
+      <c r="BO5" s="68"/>
+      <c r="BP5" s="68"/>
+      <c r="BQ5" s="68"/>
+      <c r="BR5" s="68"/>
+      <c r="BS5" s="68"/>
+      <c r="BT5" s="68"/>
+      <c r="BU5" s="68"/>
+      <c r="BV5" s="68"/>
+      <c r="BW5" s="68"/>
+      <c r="BX5" s="68"/>
+      <c r="BY5" s="68"/>
+      <c r="BZ5" s="68"/>
+      <c r="CA5" s="68"/>
+      <c r="CB5" s="68"/>
+      <c r="CC5" s="68"/>
+      <c r="CD5" s="68"/>
+      <c r="CE5" s="68"/>
+      <c r="CF5" s="68"/>
+      <c r="CG5" s="68"/>
+      <c r="CH5" s="68"/>
+      <c r="CI5" s="68"/>
+      <c r="CJ5" s="68"/>
+      <c r="CK5" s="68"/>
+      <c r="CL5" s="68"/>
+      <c r="CM5" s="68"/>
+      <c r="CN5" s="68"/>
+      <c r="CO5" s="68"/>
+      <c r="CP5" s="68"/>
+      <c r="CQ5" s="68"/>
+      <c r="CR5" s="68"/>
+      <c r="CS5" s="68"/>
+      <c r="CT5" s="68"/>
+      <c r="CU5" s="68"/>
+      <c r="CV5" s="68"/>
+      <c r="CW5" s="68"/>
+      <c r="CX5" s="68"/>
+      <c r="CY5" s="68"/>
+      <c r="CZ5" s="68"/>
+      <c r="DA5" s="68">
+        <v>6</v>
+      </c>
+      <c r="DB5" s="68"/>
+      <c r="DC5" s="68"/>
+      <c r="DD5" s="68"/>
+      <c r="DE5" s="68"/>
+      <c r="DF5" s="68"/>
+      <c r="DG5" s="68"/>
+      <c r="DH5" s="68"/>
+      <c r="DI5" s="68"/>
+      <c r="DJ5" s="68"/>
+      <c r="DK5" s="68"/>
+      <c r="DL5" s="68"/>
+      <c r="DM5" s="68"/>
+      <c r="DN5" s="68"/>
+      <c r="DO5" s="68"/>
+      <c r="DP5" s="68"/>
+      <c r="DQ5" s="68"/>
+      <c r="DR5" s="68"/>
+      <c r="DS5" s="68"/>
+      <c r="DT5" s="68"/>
+      <c r="DU5" s="68"/>
+      <c r="DV5" s="68"/>
+      <c r="DW5" s="68"/>
+      <c r="DX5" s="68"/>
+      <c r="DY5" s="68"/>
+      <c r="DZ5" s="68"/>
+      <c r="EA5" s="68"/>
+      <c r="EB5" s="68"/>
+      <c r="EC5" s="68"/>
+      <c r="ED5" s="68"/>
+      <c r="EE5" s="68"/>
+      <c r="EF5" s="68"/>
+      <c r="EG5" s="68"/>
+      <c r="EH5" s="68"/>
+      <c r="EI5" s="68"/>
+      <c r="EJ5" s="68"/>
+      <c r="EK5" s="68"/>
+      <c r="EL5" s="68"/>
+      <c r="EM5" s="68"/>
+      <c r="EN5" s="68"/>
+      <c r="EO5" s="68"/>
+      <c r="EP5" s="68"/>
+      <c r="EQ5" s="68"/>
+      <c r="ER5" s="68"/>
+      <c r="ES5" s="68"/>
+      <c r="ET5" s="68"/>
+      <c r="EU5" s="68"/>
+      <c r="EV5" s="68"/>
+      <c r="EW5" s="68"/>
+      <c r="EX5" s="68"/>
+      <c r="EY5" s="68"/>
+      <c r="EZ5" s="68"/>
+      <c r="FA5" s="68"/>
+      <c r="FB5" s="68"/>
+      <c r="FC5" s="68"/>
+      <c r="FD5" s="68"/>
+      <c r="FE5" s="68"/>
+      <c r="FF5" s="68"/>
+      <c r="FG5" s="68"/>
+      <c r="FH5" s="68"/>
+      <c r="FI5" s="69"/>
+      <c r="FJ5" s="68"/>
+      <c r="FK5" s="69"/>
+      <c r="FL5" s="68"/>
+      <c r="FM5" s="68"/>
+      <c r="FN5" s="69"/>
+      <c r="FO5" s="69"/>
+      <c r="FP5" s="69"/>
+      <c r="FQ5" s="69"/>
+      <c r="FR5" s="69"/>
+      <c r="FS5" s="69"/>
+      <c r="FT5" s="69"/>
+      <c r="FU5" s="68"/>
+      <c r="FV5" s="68"/>
+      <c r="FW5" s="69"/>
+      <c r="FX5" s="68"/>
+      <c r="FY5" s="68"/>
+      <c r="FZ5" s="69"/>
+      <c r="GA5" s="69"/>
+      <c r="GB5" s="69"/>
+      <c r="GC5" s="68"/>
+      <c r="GD5" s="68"/>
+      <c r="GE5" s="68"/>
+      <c r="GF5" s="68"/>
+      <c r="GG5" s="68"/>
+      <c r="GH5" s="68"/>
+      <c r="GI5" s="69"/>
+      <c r="GJ5" s="68"/>
+      <c r="GK5" s="69"/>
+      <c r="GL5" s="69"/>
+      <c r="GM5" s="69"/>
+      <c r="GN5" s="69"/>
+      <c r="GO5" s="69"/>
+      <c r="GP5" s="69"/>
+      <c r="GQ5" s="68"/>
+      <c r="GR5" s="68"/>
+      <c r="GS5" s="68"/>
+      <c r="GT5" s="68"/>
+      <c r="GU5" s="69"/>
+      <c r="GV5" s="69"/>
+      <c r="GW5" s="68"/>
+      <c r="GX5" s="68"/>
+      <c r="GY5" s="68"/>
+      <c r="GZ5" s="68"/>
+      <c r="HA5" s="68"/>
+      <c r="HB5" s="68"/>
+      <c r="HC5" s="68"/>
+      <c r="HD5" s="69"/>
+      <c r="HE5" s="69"/>
+      <c r="HF5" s="69"/>
+      <c r="HG5" s="69"/>
+      <c r="HH5" s="69"/>
+      <c r="HI5" s="69"/>
+      <c r="HJ5" s="69"/>
+      <c r="HK5" s="69"/>
+      <c r="HL5" s="69"/>
+      <c r="HM5" s="69"/>
+      <c r="HN5" s="69"/>
+      <c r="HO5" s="69"/>
+      <c r="HP5" s="69"/>
+      <c r="HQ5" s="69"/>
+      <c r="HR5" s="69"/>
+      <c r="HS5" s="69"/>
+      <c r="HT5" s="69"/>
+      <c r="HU5" s="69"/>
+      <c r="HV5" s="69"/>
+      <c r="HW5" s="69"/>
+      <c r="HX5" s="69"/>
+      <c r="HY5" s="68"/>
+      <c r="HZ5" s="68"/>
+      <c r="IA5" s="68"/>
+      <c r="IB5" s="69"/>
+      <c r="IC5" s="69"/>
+      <c r="ID5" s="69"/>
+      <c r="IE5" s="69"/>
+      <c r="IF5" s="68"/>
+      <c r="IG5" s="68"/>
+      <c r="IH5" s="68"/>
+      <c r="II5" s="68"/>
+      <c r="IJ5" s="68"/>
+      <c r="IK5" s="68"/>
+      <c r="IL5" s="68"/>
+      <c r="IM5" s="68"/>
+      <c r="IN5" s="69"/>
+      <c r="IO5" s="69"/>
+      <c r="IP5" s="69"/>
+      <c r="IQ5" s="68"/>
+      <c r="IR5" s="69"/>
+      <c r="IS5" s="69"/>
+      <c r="IT5" s="68"/>
+      <c r="IU5" s="68"/>
+      <c r="IV5" s="68"/>
+      <c r="IW5" s="68"/>
+      <c r="IX5" s="69"/>
+      <c r="IY5" s="69"/>
+      <c r="IZ5" s="69"/>
+      <c r="JA5" s="68"/>
     </row>
     <row r="6" spans="1:261" s="37" customFormat="1" ht="28.5" customHeight="1">
       <c r="A6" s="36">
-        <v>19</v>
-      </c>
-      <c r="B6" s="107" t="s">
-        <v>650</v>
+        <v>17</v>
+      </c>
+      <c r="B6" s="117" t="s">
+        <v>652</v>
       </c>
       <c r="C6" s="139" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="D6" s="103" t="s">
         <v>549</v>
@@ -17755,29 +17797,25 @@
         <v>385</v>
       </c>
       <c r="G6" s="103">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="H6" s="104">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="I6" s="104"/>
-      <c r="J6" s="104">
-        <v>69</v>
-      </c>
-      <c r="K6" s="104">
-        <v>74</v>
-      </c>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
       <c r="L6" s="103">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="M6" s="104">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="N6" s="104"/>
       <c r="O6" s="104"/>
       <c r="P6" s="104"/>
       <c r="Q6" s="104" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="R6" s="105"/>
       <c r="S6" s="105"/>
@@ -17794,9 +17832,11 @@
       <c r="AD6" s="105"/>
       <c r="AE6" s="105"/>
       <c r="AF6" s="106">
-        <v>26</v>
-      </c>
-      <c r="AG6" s="106"/>
+        <v>18</v>
+      </c>
+      <c r="AG6" s="106">
+        <v>18</v>
+      </c>
       <c r="AH6" s="106"/>
       <c r="AI6" s="106"/>
       <c r="AJ6" s="106"/>
@@ -17868,9 +17908,7 @@
       <c r="CX6" s="105"/>
       <c r="CY6" s="105"/>
       <c r="CZ6" s="105"/>
-      <c r="DA6" s="105">
-        <v>16</v>
-      </c>
+      <c r="DA6" s="105"/>
       <c r="DB6" s="105"/>
       <c r="DC6" s="105"/>
       <c r="DD6" s="105"/>
@@ -17921,24 +17959,12 @@
       <c r="EW6" s="105"/>
       <c r="EX6" s="105"/>
       <c r="EY6" s="105"/>
-      <c r="EZ6" s="105" t="s">
-        <v>663</v>
-      </c>
-      <c r="FA6" s="105" t="s">
-        <v>549</v>
-      </c>
-      <c r="FB6" s="105" t="s">
-        <v>384</v>
-      </c>
-      <c r="FC6" s="105" t="s">
-        <v>651</v>
-      </c>
-      <c r="FD6" s="105">
-        <v>4</v>
-      </c>
-      <c r="FE6" s="105">
-        <v>4</v>
-      </c>
+      <c r="EZ6" s="105"/>
+      <c r="FA6" s="105"/>
+      <c r="FB6" s="105"/>
+      <c r="FC6" s="105"/>
+      <c r="FD6" s="105"/>
+      <c r="FE6" s="105"/>
       <c r="FF6" s="105"/>
       <c r="FG6" s="105"/>
       <c r="FH6" s="105"/>
@@ -17986,121 +18012,300 @@
       <c r="GX6" s="105"/>
       <c r="GY6" s="105"/>
       <c r="GZ6" s="105"/>
-      <c r="HS6" s="37">
+    </row>
+    <row r="7" spans="1:261" s="37" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A7" s="36">
+        <v>19</v>
+      </c>
+      <c r="B7" s="107" t="s">
+        <v>650</v>
+      </c>
+      <c r="C7" s="139" t="s">
+        <v>663</v>
+      </c>
+      <c r="D7" s="103" t="s">
+        <v>549</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="G7" s="103">
+        <v>143</v>
+      </c>
+      <c r="H7" s="104">
+        <v>143</v>
+      </c>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104">
+        <v>69</v>
+      </c>
+      <c r="K7" s="104">
+        <v>74</v>
+      </c>
+      <c r="L7" s="103">
+        <v>139</v>
+      </c>
+      <c r="M7" s="104">
+        <v>139</v>
+      </c>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104" t="s">
+        <v>663</v>
+      </c>
+      <c r="R7" s="105"/>
+      <c r="S7" s="105"/>
+      <c r="T7" s="105"/>
+      <c r="U7" s="105"/>
+      <c r="V7" s="105"/>
+      <c r="W7" s="105"/>
+      <c r="X7" s="105"/>
+      <c r="Y7" s="105"/>
+      <c r="Z7" s="105"/>
+      <c r="AA7" s="105"/>
+      <c r="AB7" s="105"/>
+      <c r="AC7" s="105"/>
+      <c r="AD7" s="105"/>
+      <c r="AE7" s="105"/>
+      <c r="AF7" s="106">
+        <v>26</v>
+      </c>
+      <c r="AG7" s="106"/>
+      <c r="AH7" s="106"/>
+      <c r="AI7" s="106"/>
+      <c r="AJ7" s="106"/>
+      <c r="AK7" s="106"/>
+      <c r="AL7" s="106"/>
+      <c r="AM7" s="106"/>
+      <c r="AN7" s="106"/>
+      <c r="AO7" s="106"/>
+      <c r="AP7" s="106"/>
+      <c r="AQ7" s="106"/>
+      <c r="AR7" s="106"/>
+      <c r="AS7" s="106"/>
+      <c r="AT7" s="106"/>
+      <c r="AU7" s="106"/>
+      <c r="AV7" s="106"/>
+      <c r="AW7" s="106"/>
+      <c r="AX7" s="106"/>
+      <c r="AY7" s="106"/>
+      <c r="AZ7" s="106"/>
+      <c r="BA7" s="106"/>
+      <c r="BB7" s="105"/>
+      <c r="BC7" s="105"/>
+      <c r="BD7" s="105"/>
+      <c r="BE7" s="105"/>
+      <c r="BF7" s="105"/>
+      <c r="BG7" s="105"/>
+      <c r="BH7" s="105"/>
+      <c r="BI7" s="105"/>
+      <c r="BJ7" s="105"/>
+      <c r="BK7" s="105"/>
+      <c r="BL7" s="105"/>
+      <c r="BM7" s="105"/>
+      <c r="BN7" s="105"/>
+      <c r="BO7" s="105"/>
+      <c r="BP7" s="105"/>
+      <c r="BQ7" s="105"/>
+      <c r="BR7" s="105"/>
+      <c r="BS7" s="105"/>
+      <c r="BT7" s="105"/>
+      <c r="BU7" s="105"/>
+      <c r="BV7" s="105"/>
+      <c r="BW7" s="105"/>
+      <c r="BX7" s="105"/>
+      <c r="BY7" s="105"/>
+      <c r="BZ7" s="105"/>
+      <c r="CA7" s="105"/>
+      <c r="CB7" s="105"/>
+      <c r="CC7" s="105"/>
+      <c r="CD7" s="105"/>
+      <c r="CE7" s="105"/>
+      <c r="CF7" s="105"/>
+      <c r="CG7" s="105"/>
+      <c r="CH7" s="105"/>
+      <c r="CI7" s="105"/>
+      <c r="CJ7" s="105"/>
+      <c r="CK7" s="105"/>
+      <c r="CL7" s="105"/>
+      <c r="CM7" s="105"/>
+      <c r="CN7" s="105"/>
+      <c r="CO7" s="105"/>
+      <c r="CP7" s="105"/>
+      <c r="CQ7" s="105"/>
+      <c r="CR7" s="105"/>
+      <c r="CS7" s="105"/>
+      <c r="CT7" s="105"/>
+      <c r="CU7" s="105"/>
+      <c r="CV7" s="105"/>
+      <c r="CW7" s="105"/>
+      <c r="CX7" s="105"/>
+      <c r="CY7" s="105"/>
+      <c r="CZ7" s="105"/>
+      <c r="DA7" s="105">
+        <v>16</v>
+      </c>
+      <c r="DB7" s="105"/>
+      <c r="DC7" s="105"/>
+      <c r="DD7" s="105"/>
+      <c r="DE7" s="105"/>
+      <c r="DF7" s="105"/>
+      <c r="DG7" s="105"/>
+      <c r="DH7" s="105"/>
+      <c r="DI7" s="105"/>
+      <c r="DJ7" s="105"/>
+      <c r="DK7" s="105"/>
+      <c r="DL7" s="105"/>
+      <c r="DM7" s="105"/>
+      <c r="DN7" s="105"/>
+      <c r="DO7" s="105"/>
+      <c r="DP7" s="105"/>
+      <c r="DQ7" s="105"/>
+      <c r="DR7" s="105"/>
+      <c r="DS7" s="105"/>
+      <c r="DT7" s="105"/>
+      <c r="DU7" s="105"/>
+      <c r="DV7" s="105"/>
+      <c r="DW7" s="105"/>
+      <c r="DX7" s="105"/>
+      <c r="DY7" s="105"/>
+      <c r="DZ7" s="105"/>
+      <c r="EA7" s="105"/>
+      <c r="EB7" s="105"/>
+      <c r="EC7" s="105"/>
+      <c r="ED7" s="105"/>
+      <c r="EE7" s="105"/>
+      <c r="EF7" s="105"/>
+      <c r="EG7" s="105"/>
+      <c r="EH7" s="105"/>
+      <c r="EI7" s="105"/>
+      <c r="EJ7" s="105"/>
+      <c r="EK7" s="105"/>
+      <c r="EL7" s="105"/>
+      <c r="EM7" s="105"/>
+      <c r="EN7" s="105"/>
+      <c r="EO7" s="105"/>
+      <c r="EP7" s="105"/>
+      <c r="EQ7" s="105"/>
+      <c r="ER7" s="105"/>
+      <c r="ES7" s="105"/>
+      <c r="ET7" s="105"/>
+      <c r="EU7" s="105"/>
+      <c r="EV7" s="105"/>
+      <c r="EW7" s="105"/>
+      <c r="EX7" s="105"/>
+      <c r="EY7" s="105"/>
+      <c r="EZ7" s="105" t="s">
+        <v>663</v>
+      </c>
+      <c r="FA7" s="105" t="s">
+        <v>549</v>
+      </c>
+      <c r="FB7" s="105" t="s">
+        <v>384</v>
+      </c>
+      <c r="FC7" s="105" t="s">
+        <v>651</v>
+      </c>
+      <c r="FD7" s="105">
+        <v>4</v>
+      </c>
+      <c r="FE7" s="105">
+        <v>4</v>
+      </c>
+      <c r="FF7" s="105"/>
+      <c r="FG7" s="105"/>
+      <c r="FH7" s="105"/>
+      <c r="FI7" s="105"/>
+      <c r="FJ7" s="105"/>
+      <c r="FK7" s="105"/>
+      <c r="FL7" s="105"/>
+      <c r="FM7" s="105"/>
+      <c r="FN7" s="105"/>
+      <c r="FO7" s="105"/>
+      <c r="FP7" s="105"/>
+      <c r="FQ7" s="105"/>
+      <c r="FR7" s="105"/>
+      <c r="FS7" s="105"/>
+      <c r="FT7" s="105"/>
+      <c r="FU7" s="105"/>
+      <c r="FV7" s="105"/>
+      <c r="FW7" s="105"/>
+      <c r="FX7" s="105"/>
+      <c r="FY7" s="105"/>
+      <c r="FZ7" s="105"/>
+      <c r="GA7" s="105"/>
+      <c r="GB7" s="105"/>
+      <c r="GC7" s="105"/>
+      <c r="GD7" s="105"/>
+      <c r="GE7" s="105"/>
+      <c r="GF7" s="105"/>
+      <c r="GG7" s="105"/>
+      <c r="GH7" s="105"/>
+      <c r="GI7" s="105"/>
+      <c r="GJ7" s="105"/>
+      <c r="GK7" s="105"/>
+      <c r="GL7" s="105"/>
+      <c r="GM7" s="105"/>
+      <c r="GN7" s="105"/>
+      <c r="GO7" s="105"/>
+      <c r="GP7" s="105"/>
+      <c r="GQ7" s="105"/>
+      <c r="GR7" s="105"/>
+      <c r="GS7" s="105"/>
+      <c r="GT7" s="105"/>
+      <c r="GU7" s="105"/>
+      <c r="GV7" s="105"/>
+      <c r="GW7" s="105"/>
+      <c r="GX7" s="105"/>
+      <c r="GY7" s="105"/>
+      <c r="GZ7" s="105"/>
+      <c r="HS7" s="37">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:261" ht="28.5" customHeight="1">
-      <c r="A7" s="1">
+    <row r="8" spans="1:261" ht="28.5" customHeight="1">
+      <c r="A8" s="1">
         <v>23</v>
       </c>
-      <c r="B7" s="108" t="s">
+      <c r="B8" s="108" t="s">
         <v>664</v>
       </c>
-      <c r="C7" s="110" t="s">
+      <c r="C8" s="110" t="s">
         <v>617</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>549</v>
-      </c>
-      <c r="E7" s="66" t="s">
-        <v>384</v>
-      </c>
-      <c r="F7" s="66" t="s">
-        <v>385</v>
-      </c>
-      <c r="G7" s="65">
-        <v>50</v>
-      </c>
-      <c r="H7" s="65">
-        <v>50</v>
-      </c>
-      <c r="L7" s="65">
-        <v>50</v>
-      </c>
-      <c r="M7" s="65">
-        <v>50</v>
-      </c>
-      <c r="Q7" s="65" t="s">
-        <v>617</v>
-      </c>
-      <c r="AF7" s="68">
-        <v>12</v>
-      </c>
-      <c r="AG7" s="68"/>
-      <c r="AH7" s="68"/>
-      <c r="AI7" s="68"/>
-      <c r="AJ7" s="68"/>
-      <c r="AK7" s="68"/>
-      <c r="AL7" s="68"/>
-      <c r="AM7" s="68"/>
-      <c r="AN7" s="68"/>
-      <c r="AO7" s="68"/>
-      <c r="AP7" s="68"/>
-      <c r="AQ7" s="68"/>
-      <c r="AR7" s="68"/>
-      <c r="AS7" s="68"/>
-      <c r="AT7" s="68"/>
-      <c r="AU7" s="68"/>
-      <c r="AV7" s="68"/>
-      <c r="AW7" s="68"/>
-      <c r="AX7" s="68"/>
-      <c r="AY7" s="68"/>
-      <c r="AZ7" s="68"/>
-      <c r="BA7" s="68"/>
-    </row>
-    <row r="8" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A8" s="1">
-        <v>30</v>
-      </c>
-      <c r="B8" s="107" t="s">
-        <v>666</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>639</v>
       </c>
       <c r="D8" s="65" t="s">
         <v>549</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F8" s="66" t="s">
         <v>385</v>
       </c>
       <c r="G8" s="65">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="H8" s="65">
-        <v>58</v>
-      </c>
-      <c r="I8" s="65" t="s">
-        <v>728</v>
-      </c>
-      <c r="J8" s="65">
-        <v>25</v>
-      </c>
-      <c r="K8" s="65">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="L8" s="65">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M8" s="65">
-        <v>58</v>
-      </c>
-      <c r="N8" s="65"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="82"/>
-      <c r="Q8" s="66" t="s">
-        <v>739</v>
+        <v>50</v>
+      </c>
+      <c r="Q8" s="65" t="s">
+        <v>617</v>
       </c>
       <c r="AF8" s="68">
-        <v>10</v>
-      </c>
-      <c r="AG8" s="68">
-        <v>10</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="AG8" s="68"/>
       <c r="AH8" s="68"/>
       <c r="AI8" s="68"/>
       <c r="AJ8" s="68"/>
@@ -18108,9 +18313,7 @@
       <c r="AL8" s="68"/>
       <c r="AM8" s="68"/>
       <c r="AN8" s="68"/>
-      <c r="AO8" s="68">
-        <v>5</v>
-      </c>
+      <c r="AO8" s="68"/>
       <c r="AP8" s="68"/>
       <c r="AQ8" s="68"/>
       <c r="AR8" s="68"/>
@@ -18123,138 +18326,150 @@
       <c r="AY8" s="68"/>
       <c r="AZ8" s="68"/>
       <c r="BA8" s="68"/>
-      <c r="BE8" s="66">
-        <v>4</v>
-      </c>
-      <c r="CF8" s="66">
-        <v>2</v>
-      </c>
-      <c r="CH8" s="66">
-        <v>1</v>
-      </c>
-      <c r="CV8" s="66">
-        <v>2</v>
-      </c>
-      <c r="DA8" s="66">
-        <v>1</v>
-      </c>
-      <c r="DC8" s="66">
-        <v>1</v>
-      </c>
-      <c r="EZ8" s="66" t="s">
-        <v>639</v>
-      </c>
-      <c r="FA8" s="66" t="s">
-        <v>549</v>
-      </c>
-      <c r="FB8" s="66" t="s">
-        <v>385</v>
-      </c>
-      <c r="FC8" s="66" t="s">
-        <v>646</v>
-      </c>
-      <c r="FD8" s="66">
-        <v>35</v>
-      </c>
-      <c r="FE8" s="66">
-        <v>58</v>
-      </c>
-      <c r="FP8" s="66">
-        <v>13</v>
-      </c>
-      <c r="FQ8" s="66">
-        <v>11</v>
-      </c>
-      <c r="FV8" s="66">
-        <v>3</v>
-      </c>
-      <c r="GG8" s="66">
-        <v>2</v>
-      </c>
-      <c r="GJ8" s="66">
-        <v>1</v>
-      </c>
-      <c r="HS8" s="66">
-        <v>2</v>
-      </c>
-      <c r="HY8" s="66">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A9" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B9" s="107" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C9" s="110" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="D9" s="65" t="s">
         <v>549</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F9" s="66" t="s">
         <v>385</v>
       </c>
       <c r="G9" s="65">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="H9" s="65">
-        <v>119</v>
-      </c>
-      <c r="I9" s="65">
-        <v>62.1</v>
+        <v>58</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>728</v>
       </c>
       <c r="J9" s="65">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="K9" s="65">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="L9" s="65">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="M9" s="65">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="N9" s="65"/>
       <c r="O9" s="65"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65" t="s">
-        <v>617</v>
-      </c>
-      <c r="AF9" s="66">
-        <v>17</v>
-      </c>
-      <c r="AG9" s="66">
-        <v>15</v>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="66" t="s">
+        <v>739</v>
+      </c>
+      <c r="AF9" s="68">
+        <v>10</v>
+      </c>
+      <c r="AG9" s="68">
+        <v>10</v>
+      </c>
+      <c r="AH9" s="68"/>
+      <c r="AI9" s="68"/>
+      <c r="AJ9" s="68"/>
+      <c r="AK9" s="68"/>
+      <c r="AL9" s="68"/>
+      <c r="AM9" s="68"/>
+      <c r="AN9" s="68"/>
+      <c r="AO9" s="68">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="68"/>
+      <c r="AQ9" s="68"/>
+      <c r="AR9" s="68"/>
+      <c r="AS9" s="68"/>
+      <c r="AT9" s="68"/>
+      <c r="AU9" s="68"/>
+      <c r="AV9" s="68"/>
+      <c r="AW9" s="68"/>
+      <c r="AX9" s="68"/>
+      <c r="AY9" s="68"/>
+      <c r="AZ9" s="68"/>
+      <c r="BA9" s="68"/>
+      <c r="BE9" s="66">
+        <v>4</v>
+      </c>
+      <c r="CF9" s="66">
+        <v>2</v>
+      </c>
+      <c r="CH9" s="66">
+        <v>1</v>
+      </c>
+      <c r="CV9" s="66">
+        <v>2</v>
       </c>
       <c r="DA9" s="66">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="DC9" s="66">
         <v>1</v>
       </c>
-      <c r="DD9" s="66">
-        <v>7</v>
-      </c>
-      <c r="GU9" s="97"/>
+      <c r="EZ9" s="66" t="s">
+        <v>639</v>
+      </c>
+      <c r="FA9" s="66" t="s">
+        <v>549</v>
+      </c>
+      <c r="FB9" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="FC9" s="66" t="s">
+        <v>646</v>
+      </c>
+      <c r="FD9" s="66">
+        <v>35</v>
+      </c>
+      <c r="FE9" s="66">
+        <v>58</v>
+      </c>
+      <c r="FP9" s="66">
+        <v>13</v>
+      </c>
+      <c r="FQ9" s="66">
+        <v>11</v>
+      </c>
+      <c r="FV9" s="66">
+        <v>3</v>
+      </c>
+      <c r="GG9" s="66">
+        <v>2</v>
+      </c>
+      <c r="GJ9" s="66">
+        <v>1</v>
+      </c>
+      <c r="HS9" s="66">
+        <v>2</v>
+      </c>
+      <c r="HY9" s="66">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A10" s="70">
-        <v>43</v>
-      </c>
-      <c r="B10" s="111" t="s">
-        <v>669</v>
-      </c>
-      <c r="C10" s="112" t="s">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10" s="107" t="s">
+        <v>668</v>
+      </c>
+      <c r="C10" s="110" t="s">
         <v>617</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="65" t="s">
         <v>549</v>
       </c>
       <c r="E10" s="66" t="s">
@@ -18264,23 +18479,25 @@
         <v>385</v>
       </c>
       <c r="G10" s="65">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="H10" s="65">
-        <v>79</v>
-      </c>
-      <c r="I10" s="65"/>
+        <v>119</v>
+      </c>
+      <c r="I10" s="65">
+        <v>62.1</v>
+      </c>
       <c r="J10" s="65">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K10" s="65">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L10" s="65">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="M10" s="65">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="N10" s="65"/>
       <c r="O10" s="65"/>
@@ -18289,181 +18506,153 @@
         <v>617</v>
       </c>
       <c r="AF10" s="66">
-        <v>33</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AG10" s="66">
+        <v>15</v>
+      </c>
+      <c r="DA10" s="66">
+        <v>12</v>
+      </c>
+      <c r="DC10" s="66">
+        <v>1</v>
+      </c>
+      <c r="DD10" s="66">
+        <v>7</v>
+      </c>
+      <c r="GU10" s="97"/>
     </row>
     <row r="11" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A11" s="1">
-        <v>50</v>
-      </c>
-      <c r="B11" s="108" t="s">
-        <v>670</v>
-      </c>
-      <c r="C11" s="110" t="s">
+      <c r="A11" s="70">
+        <v>43</v>
+      </c>
+      <c r="B11" s="111" t="s">
+        <v>669</v>
+      </c>
+      <c r="C11" s="112" t="s">
         <v>617</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="66" t="s">
         <v>549</v>
       </c>
       <c r="E11" s="66" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F11" s="66" t="s">
         <v>385</v>
       </c>
       <c r="G11" s="65">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="H11" s="65">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
+      <c r="J11" s="65">
+        <v>42</v>
+      </c>
+      <c r="K11" s="65">
+        <v>37</v>
+      </c>
       <c r="L11" s="65">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M11" s="65">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N11" s="65"/>
       <c r="O11" s="65"/>
       <c r="P11" s="65"/>
-      <c r="Q11" s="66" t="s">
+      <c r="Q11" s="65" t="s">
         <v>617</v>
       </c>
-      <c r="DA11" s="66">
+      <c r="AF11" s="66">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A12" s="1">
+        <v>50</v>
+      </c>
+      <c r="B12" s="108" t="s">
+        <v>670</v>
+      </c>
+      <c r="C12" s="110" t="s">
+        <v>617</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>549</v>
+      </c>
+      <c r="E12" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="F12" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="G12" s="65">
+        <v>132</v>
+      </c>
+      <c r="H12" s="65">
+        <v>105</v>
+      </c>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65">
+        <v>84</v>
+      </c>
+      <c r="M12" s="65">
+        <v>84</v>
+      </c>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="66" t="s">
+        <v>617</v>
+      </c>
+      <c r="DA12" s="66">
         <v>7</v>
       </c>
-      <c r="DB11" s="66">
+      <c r="DB12" s="66">
         <v>3</v>
       </c>
-      <c r="DC11" s="66">
+      <c r="DC12" s="66">
         <v>3</v>
       </c>
-      <c r="EZ11" s="66" t="s">
+      <c r="EZ12" s="66" t="s">
         <v>617</v>
       </c>
-      <c r="FA11" s="66" t="s">
+      <c r="FA12" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="FB11" s="66" t="s">
+      <c r="FB12" s="66" t="s">
         <v>385</v>
       </c>
-      <c r="FC11" s="66" t="s">
+      <c r="FC12" s="66" t="s">
         <v>631</v>
       </c>
-      <c r="FD11" s="66">
+      <c r="FD12" s="66">
         <v>48</v>
       </c>
-      <c r="FE11" s="66">
+      <c r="FE12" s="66">
         <v>48</v>
       </c>
-      <c r="HS11" s="66">
+      <c r="HS12" s="66">
         <v>3</v>
       </c>
-      <c r="HU11" s="66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:261" ht="28.5" customHeight="1">
-      <c r="A12" s="1">
-        <v>60</v>
-      </c>
-      <c r="B12" s="108" t="s">
-        <v>671</v>
-      </c>
-      <c r="C12" s="113" t="s">
-        <v>617</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>549</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G12" s="50">
-        <v>312</v>
-      </c>
-      <c r="H12" s="65">
-        <v>312</v>
-      </c>
-      <c r="L12" s="65">
-        <v>268</v>
-      </c>
-      <c r="M12" s="65">
-        <v>268</v>
-      </c>
-      <c r="Q12" s="65" t="s">
-        <v>617</v>
-      </c>
-      <c r="AF12" s="67">
-        <v>83</v>
-      </c>
-      <c r="AG12" s="67">
-        <v>76</v>
-      </c>
-      <c r="AR12" s="67">
-        <v>2</v>
-      </c>
-      <c r="DA12" s="67">
-        <v>16</v>
-      </c>
-      <c r="DB12" s="67">
-        <v>1</v>
-      </c>
-      <c r="DC12" s="67">
-        <v>9</v>
-      </c>
-      <c r="DD12" s="67">
-        <v>2</v>
-      </c>
-      <c r="EZ12" s="67" t="s">
-        <v>617</v>
-      </c>
-      <c r="FA12" s="67" t="s">
-        <v>549</v>
-      </c>
-      <c r="FB12" s="67" t="s">
-        <v>384</v>
-      </c>
-      <c r="FC12" s="67" t="s">
-        <v>631</v>
-      </c>
-      <c r="FD12" s="67">
-        <v>44</v>
-      </c>
-      <c r="FE12" s="67">
-        <v>44</v>
-      </c>
-      <c r="FP12" s="67">
-        <v>14</v>
-      </c>
-      <c r="FQ12" s="67">
-        <v>12</v>
-      </c>
-      <c r="HS12" s="2">
-        <v>4</v>
-      </c>
-      <c r="HU12" s="2">
-        <v>1</v>
-      </c>
-      <c r="HV12" s="2">
+      <c r="HU12" s="66">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:261" ht="28.5" customHeight="1">
       <c r="A13" s="1">
-        <v>62</v>
-      </c>
-      <c r="B13" s="107" t="s">
-        <v>672</v>
+        <v>60</v>
+      </c>
+      <c r="B13" s="108" t="s">
+        <v>671</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>549</v>
@@ -18475,28 +18664,40 @@
         <v>385</v>
       </c>
       <c r="G13" s="50">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="H13" s="65">
-        <v>335</v>
-      </c>
-      <c r="J13" s="65">
-        <v>169</v>
-      </c>
-      <c r="K13" s="65">
-        <v>166</v>
+        <v>312</v>
       </c>
       <c r="L13" s="65">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="M13" s="65">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="Q13" s="65" t="s">
         <v>617</v>
       </c>
-      <c r="CF13" s="67">
-        <v>34</v>
+      <c r="AF13" s="67">
+        <v>83</v>
+      </c>
+      <c r="AG13" s="67">
+        <v>76</v>
+      </c>
+      <c r="AR13" s="67">
+        <v>2</v>
+      </c>
+      <c r="DA13" s="67">
+        <v>16</v>
+      </c>
+      <c r="DB13" s="67">
+        <v>1</v>
+      </c>
+      <c r="DC13" s="67">
+        <v>9</v>
+      </c>
+      <c r="DD13" s="67">
+        <v>2</v>
       </c>
       <c r="EZ13" s="67" t="s">
         <v>617</v>
@@ -18508,85 +18709,104 @@
         <v>384</v>
       </c>
       <c r="FC13" s="67" t="s">
+        <v>631</v>
+      </c>
+      <c r="FD13" s="67">
+        <v>44</v>
+      </c>
+      <c r="FE13" s="67">
+        <v>44</v>
+      </c>
+      <c r="FP13" s="67">
+        <v>14</v>
+      </c>
+      <c r="FQ13" s="67">
+        <v>12</v>
+      </c>
+      <c r="HS13" s="2">
+        <v>4</v>
+      </c>
+      <c r="HU13" s="2">
+        <v>1</v>
+      </c>
+      <c r="HV13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:261" ht="28.5" customHeight="1">
+      <c r="A14" s="1">
+        <v>62</v>
+      </c>
+      <c r="B14" s="107" t="s">
+        <v>672</v>
+      </c>
+      <c r="C14" s="113" t="s">
+        <v>629</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G14" s="50">
+        <v>335</v>
+      </c>
+      <c r="H14" s="65">
+        <v>335</v>
+      </c>
+      <c r="J14" s="65">
+        <v>169</v>
+      </c>
+      <c r="K14" s="65">
+        <v>166</v>
+      </c>
+      <c r="L14" s="65">
+        <v>284</v>
+      </c>
+      <c r="M14" s="65">
+        <v>284</v>
+      </c>
+      <c r="Q14" s="65" t="s">
+        <v>617</v>
+      </c>
+      <c r="CF14" s="67">
+        <v>34</v>
+      </c>
+      <c r="EZ14" s="67" t="s">
+        <v>617</v>
+      </c>
+      <c r="FA14" s="67" t="s">
+        <v>549</v>
+      </c>
+      <c r="FB14" s="67" t="s">
+        <v>384</v>
+      </c>
+      <c r="FC14" s="67" t="s">
         <v>630</v>
       </c>
-      <c r="FD13" s="67">
+      <c r="FD14" s="67">
         <v>51</v>
       </c>
-      <c r="FE13" s="67">
+      <c r="FE14" s="67">
         <v>51</v>
       </c>
-      <c r="HA13" s="2">
+      <c r="HA14" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A14" s="70">
-        <v>93</v>
-      </c>
-      <c r="B14" s="108" t="s">
-        <v>684</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>685</v>
-      </c>
-      <c r="D14" s="65" t="s">
-        <v>549</v>
-      </c>
-      <c r="E14" s="66" t="s">
-        <v>384</v>
-      </c>
-      <c r="F14" s="66" t="s">
-        <v>384</v>
-      </c>
-      <c r="G14" s="65">
-        <v>51</v>
-      </c>
-      <c r="H14" s="65">
-        <v>51</v>
-      </c>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65">
-        <v>17</v>
-      </c>
-      <c r="K14" s="65">
-        <v>34</v>
-      </c>
-      <c r="L14" s="65">
-        <v>51</v>
-      </c>
-      <c r="M14" s="65">
-        <v>51</v>
-      </c>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="66" t="s">
-        <v>685</v>
-      </c>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="DA14" s="66">
-        <v>10</v>
-      </c>
-      <c r="FF14" s="70"/>
-      <c r="FG14" s="70"/>
-      <c r="FH14" s="70"/>
     </row>
     <row r="15" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A15" s="70">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>617</v>
+        <v>685</v>
       </c>
       <c r="D15" s="65" t="s">
         <v>549</v>
@@ -18598,61 +18818,103 @@
         <v>384</v>
       </c>
       <c r="G15" s="65">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="H15" s="65">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="I15" s="65"/>
       <c r="J15" s="65">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K15" s="65">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="L15" s="65">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="M15" s="65">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="N15" s="65"/>
       <c r="O15" s="65"/>
       <c r="P15" s="65"/>
-      <c r="Q15" s="65" t="s">
+      <c r="Q15" s="66" t="s">
+        <v>685</v>
+      </c>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="DA15" s="66">
+        <v>10</v>
+      </c>
+      <c r="FF15" s="70"/>
+      <c r="FG15" s="70"/>
+      <c r="FH15" s="70"/>
+    </row>
+    <row r="16" spans="1:261" s="66" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A16" s="70">
+        <v>97</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>689</v>
+      </c>
+      <c r="C16" s="66" t="s">
         <v>617</v>
       </c>
-      <c r="AF15" s="66">
+      <c r="D16" s="65" t="s">
+        <v>549</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="G16" s="65">
+        <v>92</v>
+      </c>
+      <c r="H16" s="65">
+        <v>92</v>
+      </c>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65">
+        <v>40</v>
+      </c>
+      <c r="K16" s="65">
+        <v>52</v>
+      </c>
+      <c r="L16" s="65">
+        <v>92</v>
+      </c>
+      <c r="M16" s="65">
+        <v>92</v>
+      </c>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65" t="s">
+        <v>617</v>
+      </c>
+      <c r="AF16" s="66">
         <v>24</v>
       </c>
-      <c r="CF15" s="66">
+      <c r="CF16" s="66">
         <v>3</v>
       </c>
-      <c r="DA15" s="66">
+      <c r="DA16" s="66">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:261" ht="28.5" customHeight="1">
-      <c r="A16" s="70"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="67"/>
-      <c r="G16" s="65"/>
-    </row>
-    <row r="17" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="17" spans="1:17" ht="28.5" customHeight="1">
       <c r="A17" s="70"/>
-      <c r="B17" s="108"/>
-      <c r="D17" s="65"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="67"/>
       <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
     </row>
     <row r="18" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A18" s="70"/>
@@ -18670,9 +18932,21 @@
       <c r="P18" s="65"/>
       <c r="Q18" s="65"/>
     </row>
-    <row r="19" spans="1:17" ht="28.5" customHeight="1">
+    <row r="19" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A19" s="70"/>
-      <c r="C19" s="67"/>
+      <c r="B19" s="108"/>
+      <c r="D19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
     </row>
     <row r="20" spans="1:17" ht="28.5" customHeight="1">
       <c r="A20" s="70"/>
@@ -18690,32 +18964,17 @@
       <c r="A23" s="70"/>
       <c r="C23" s="67"/>
     </row>
-    <row r="24" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="24" spans="1:17" ht="28.5" customHeight="1">
       <c r="A24" s="70"/>
-      <c r="B24" s="108"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="65"/>
-      <c r="P24" s="65"/>
-      <c r="Q24" s="65"/>
+      <c r="C24" s="67"/>
     </row>
     <row r="25" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A25" s="70"/>
       <c r="B25" s="108"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
       <c r="G25" s="65"/>
       <c r="H25" s="65"/>
       <c r="I25" s="65"/>
@@ -18728,47 +18987,62 @@
       <c r="P25" s="65"/>
       <c r="Q25" s="65"/>
     </row>
-    <row r="26" spans="1:17" ht="28.5" customHeight="1">
+    <row r="26" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A26" s="70"/>
-      <c r="C26" s="67"/>
+      <c r="B26" s="108"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
     </row>
     <row r="27" spans="1:17" ht="28.5" customHeight="1">
       <c r="A27" s="70"/>
       <c r="C27" s="67"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="138"/>
-    </row>
-    <row r="28" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
+    </row>
+    <row r="28" spans="1:17" ht="28.5" customHeight="1">
       <c r="A28" s="70"/>
-      <c r="B28" s="108"/>
-      <c r="D28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="65"/>
-    </row>
-    <row r="29" spans="1:17" ht="28.5" customHeight="1">
+      <c r="C28" s="67"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="87"/>
+      <c r="O28" s="87"/>
+      <c r="P28" s="87"/>
+      <c r="Q28" s="138"/>
+    </row>
+    <row r="29" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A29" s="70"/>
-      <c r="C29" s="67"/>
+      <c r="B29" s="108"/>
+      <c r="D29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="65"/>
     </row>
     <row r="30" spans="1:17" ht="28.5" customHeight="1">
       <c r="A30" s="70"/>
@@ -18778,25 +19052,25 @@
       <c r="A31" s="70"/>
       <c r="C31" s="67"/>
     </row>
-    <row r="32" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="32" spans="1:17" ht="28.5" customHeight="1">
       <c r="A32" s="70"/>
-      <c r="B32" s="108"/>
-      <c r="D32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-    </row>
-    <row r="33" spans="1:45" ht="28.5" customHeight="1">
+      <c r="C32" s="67"/>
+    </row>
+    <row r="33" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A33" s="70"/>
-      <c r="C33" s="67"/>
+      <c r="B33" s="108"/>
+      <c r="D33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="65"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="65"/>
     </row>
     <row r="34" spans="1:45" ht="28.5" customHeight="1">
       <c r="A34" s="70"/>
@@ -18826,80 +19100,74 @@
       <c r="A40" s="70"/>
       <c r="C40" s="67"/>
     </row>
-    <row r="41" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="41" spans="1:45" ht="28.5" customHeight="1">
       <c r="A41" s="70"/>
-      <c r="B41" s="108"/>
-      <c r="D41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="65"/>
-      <c r="N41" s="65"/>
-      <c r="O41" s="65"/>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="65"/>
-    </row>
-    <row r="42" spans="1:45" ht="28.5" customHeight="1">
+      <c r="C41" s="67"/>
+    </row>
+    <row r="42" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A42" s="70"/>
-      <c r="C42" s="67"/>
+      <c r="B42" s="108"/>
+      <c r="D42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
     </row>
     <row r="43" spans="1:45" ht="28.5" customHeight="1">
       <c r="A43" s="70"/>
       <c r="C43" s="67"/>
     </row>
-    <row r="44" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="44" spans="1:45" ht="28.5" customHeight="1">
       <c r="A44" s="70"/>
-      <c r="B44" s="108"/>
-      <c r="D44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="65"/>
-      <c r="O44" s="65"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-    </row>
-    <row r="45" spans="1:45" ht="28.5" customHeight="1">
+      <c r="C44" s="67"/>
+    </row>
+    <row r="45" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A45" s="70"/>
-      <c r="C45" s="67"/>
-    </row>
-    <row r="46" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
+      <c r="B45" s="108"/>
+      <c r="D45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="65"/>
+    </row>
+    <row r="46" spans="1:45" ht="28.5" customHeight="1">
       <c r="A46" s="70"/>
-      <c r="B46" s="110"/>
-      <c r="D46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="AK46" s="94"/>
-    </row>
-    <row r="47" spans="1:45" ht="28.5" customHeight="1">
+      <c r="C46" s="67"/>
+    </row>
+    <row r="47" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A47" s="70"/>
-      <c r="C47" s="66"/>
-      <c r="AM47" s="68"/>
-      <c r="AN47" s="68"/>
-      <c r="AO47" s="68"/>
-      <c r="AP47" s="68"/>
-      <c r="AQ47" s="68"/>
-      <c r="AR47" s="68"/>
-      <c r="AS47" s="68"/>
+      <c r="B47" s="110"/>
+      <c r="D47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
+      <c r="AK47" s="94"/>
     </row>
     <row r="48" spans="1:45" ht="28.5" customHeight="1">
       <c r="A48" s="70"/>
+      <c r="C48" s="66"/>
       <c r="AM48" s="68"/>
       <c r="AN48" s="68"/>
       <c r="AO48" s="68"/>
@@ -18908,41 +19176,35 @@
       <c r="AR48" s="68"/>
       <c r="AS48" s="68"/>
     </row>
-    <row r="49" spans="1:17" ht="28.5" customHeight="1">
-      <c r="C49" s="67"/>
-    </row>
-    <row r="50" spans="1:17" ht="28.5" customHeight="1">
+    <row r="49" spans="1:45" ht="28.5" customHeight="1">
+      <c r="A49" s="70"/>
+      <c r="AM49" s="68"/>
+      <c r="AN49" s="68"/>
+      <c r="AO49" s="68"/>
+      <c r="AP49" s="68"/>
+      <c r="AQ49" s="68"/>
+      <c r="AR49" s="68"/>
+      <c r="AS49" s="68"/>
+    </row>
+    <row r="50" spans="1:45" ht="28.5" customHeight="1">
       <c r="C50" s="67"/>
     </row>
-    <row r="51" spans="1:17" ht="28.5" customHeight="1">
+    <row r="51" spans="1:45" ht="28.5" customHeight="1">
       <c r="C51" s="67"/>
     </row>
-    <row r="52" spans="1:17" ht="28.5" customHeight="1">
+    <row r="52" spans="1:45" ht="28.5" customHeight="1">
       <c r="C52" s="67"/>
     </row>
-    <row r="53" spans="1:17" ht="28.5" customHeight="1">
+    <row r="53" spans="1:45" ht="28.5" customHeight="1">
       <c r="C53" s="67"/>
     </row>
-    <row r="54" spans="1:17" ht="28.5" customHeight="1">
+    <row r="54" spans="1:45" ht="28.5" customHeight="1">
       <c r="C54" s="67"/>
     </row>
-    <row r="55" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="108"/>
-      <c r="D55" s="65"/>
-      <c r="G55" s="65"/>
-      <c r="H55" s="65"/>
-      <c r="I55" s="65"/>
-      <c r="J55" s="65"/>
-      <c r="K55" s="65"/>
-      <c r="L55" s="65"/>
-      <c r="M55" s="65"/>
-      <c r="N55" s="65"/>
-      <c r="O55" s="65"/>
-      <c r="P55" s="65"/>
-      <c r="Q55" s="65"/>
-    </row>
-    <row r="56" spans="1:17" s="66" customFormat="1" ht="28.5" customHeight="1">
+    <row r="55" spans="1:45" ht="28.5" customHeight="1">
+      <c r="C55" s="67"/>
+    </row>
+    <row r="56" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="108"/>
       <c r="D56" s="65"/>
@@ -18957,6 +19219,22 @@
       <c r="O56" s="65"/>
       <c r="P56" s="65"/>
       <c r="Q56" s="65"/>
+    </row>
+    <row r="57" spans="1:45" s="66" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="108"/>
+      <c r="D57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="65"/>
+      <c r="M57" s="65"/>
+      <c r="N57" s="65"/>
+      <c r="O57" s="65"/>
+      <c r="P57" s="65"/>
+      <c r="Q57" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -18983,17 +19261,17 @@
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C24:F24">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  <conditionalFormatting sqref="C25:F25">
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:F25">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+  <conditionalFormatting sqref="C26:F26">
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Sheen+YS&amp;cauthor_id=25767048" xr:uid="{9783B5A2-B2D3-4668-B90F-AE901315D29B}"/>
-    <hyperlink ref="B13" r:id="rId2" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Kong+Y&amp;cauthor_id=21325067" xr:uid="{1C7FA9EE-079E-44DD-9160-0031F7344018}"/>
-    <hyperlink ref="B8" r:id="rId3" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Kaji+T&amp;cauthor_id=27771229" xr:uid="{9AE8EA73-29BC-448B-9A2F-326CFFF405B0}"/>
-    <hyperlink ref="B6" r:id="rId4" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Lee+SH&amp;cauthor_id=29361821" xr:uid="{5DAC2F63-3780-4454-B5E7-EA3D1F7B9955}"/>
+    <hyperlink ref="B10" r:id="rId1" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Sheen+YS&amp;cauthor_id=25767048" xr:uid="{9783B5A2-B2D3-4668-B90F-AE901315D29B}"/>
+    <hyperlink ref="B14" r:id="rId2" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Kong+Y&amp;cauthor_id=21325067" xr:uid="{1C7FA9EE-079E-44DD-9160-0031F7344018}"/>
+    <hyperlink ref="B9" r:id="rId3" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Kaji+T&amp;cauthor_id=27771229" xr:uid="{9AE8EA73-29BC-448B-9A2F-326CFFF405B0}"/>
+    <hyperlink ref="B7" r:id="rId4" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Lee+SH&amp;cauthor_id=29361821" xr:uid="{5DAC2F63-3780-4454-B5E7-EA3D1F7B9955}"/>
     <hyperlink ref="B3" r:id="rId5" display="https://pubmed-ncbi-nlm-nih-gov.proxy.insermbiblio.inist.fr/?term=Sheen+YS&amp;cauthor_id=31408190" xr:uid="{999E0C2F-C8B5-416C-868C-99A12E2C9520}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
